--- a/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_answers.xlsx
+++ b/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_answers.xlsx
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1</v>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1666</v>
+        <v>1500</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>2</v>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1</v>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>108.75</v>
+        <v>100</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3</v>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1</v>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>1</v>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>1</v>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1</v>

--- a/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_answers.xlsx
+++ b/datasets/day1_excel_foundations/04_formulas_fundamentals/d1_m4_formulas_answers.xlsx
@@ -657,7 +657,7 @@
         <v>1500</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
         <f>C9*D9</f>
@@ -695,7 +695,7 @@
         <v>1400</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6">
         <f>C10*D10</f>
@@ -726,11 +726,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1</v>
@@ -764,11 +764,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2</v>
@@ -802,14 +802,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6">
         <f>C13*D13</f>
@@ -878,14 +878,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6">
         <f>C15*D15</f>
@@ -916,14 +916,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="6">
         <f>C16*D16</f>
@@ -954,14 +954,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="6">
         <f>C17*D17</f>
@@ -992,11 +992,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1</v>
@@ -1030,14 +1030,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6">
         <f>C19*D19</f>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1</v>
@@ -1106,11 +1106,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -1144,11 +1144,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -1182,11 +1182,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -1220,14 +1220,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="6">
         <f>C24*D24</f>
@@ -1258,14 +1258,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="6">
         <f>C25*D25</f>
@@ -1296,11 +1296,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1</v>
